--- a/exports/player_elo_table.xlsx
+++ b/exports/player_elo_table.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B48"/>
+  <dimension ref="A1:B58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,562 +443,682 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Kevin Lee</t>
+          <t>Noah Dale</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1571</t>
+          <t>997</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Aaron Carter</t>
+          <t>Kevin Lee</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1385</t>
+          <t>1571</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Roman Ramirez</t>
+          <t>Aaron Carter</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1376</t>
+          <t>1385</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Rohan Chowla</t>
+          <t>Roman Ramirez</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1339</t>
+          <t>1376</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Kevin Cooper</t>
+          <t>Milen Satish</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1352</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Autumn Hong</t>
+          <t>Rohan Chowla</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1339</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Nathan Snow</t>
+          <t>Ryan Healy</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1307</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Milen Satish</t>
+          <t>Kevin Cooper</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1245</t>
+          <t>1272</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Will Simpson</t>
+          <t>Autumn Hong</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1244</t>
+          <t>1272</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Luke Woods</t>
+          <t>Nathan Snow</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1241</t>
+          <t>1270</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Matthew Rusten</t>
+          <t>Bryce Taylor</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1238</t>
+          <t>1265</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Eric Edwards</t>
+          <t>Cason Duszak</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1234</t>
+          <t>1252</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Coby Lovelace</t>
+          <t>Will Simpson</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1231</t>
+          <t>1244</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Matthew Werfel</t>
+          <t>Luke Woods</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1231</t>
+          <t>1241</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Matthew Kish</t>
+          <t>Matthew Rusten</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1229</t>
+          <t>1238</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Jack Massingill</t>
+          <t>Matthew Kish</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1228</t>
+          <t>1235</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Leah Baetcke</t>
+          <t>Coby Lovelace</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1217</t>
+          <t>1231</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Kristian Banlaoi</t>
+          <t>Jack Massingill</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>1228</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Bryce Taylor</t>
+          <t>Eric Edwards</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1212</t>
+          <t>1226</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ann Hall</t>
+          <t>Leah Baetcke</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>1217</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Carolyn LastName</t>
+          <t>Kristian Banlaoi</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1207</t>
+          <t>1216</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Yvonne Nguyen</t>
+          <t>Matthew Werfel</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1205</t>
+          <t>1215</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Connor Rogers</t>
+          <t>Ann Hall</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1202</t>
+          <t>1210</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gabe Silverstein</t>
+          <t>Rasmi Tangirala</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1201</t>
+          <t>1210</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Cason Duszak</t>
+          <t>Connor Rogers</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1199</t>
+          <t>1208</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Carla Betancourt</t>
+          <t>Carolyn LastName</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1192</t>
+          <t>1207</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Yafu LastName</t>
+          <t>Yvonne Nguyen</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1205</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Anna Brown</t>
+          <t>Gabe Silverstein</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1176</t>
+          <t>1201</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Jason Jackson</t>
+          <t>Carla Betancourt</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1176</t>
+          <t>1192</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Ronan McKinney</t>
+          <t>Benjamin Merkel</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1173</t>
+          <t>1192</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Charles Myersberg</t>
+          <t>Victoria LastName</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>1191</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Rasmi Tangirala</t>
+          <t>Yafu LastName</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>1187</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Alex LastName</t>
+          <t>Maria Stalcup</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1161</t>
+          <t>1184</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Reagan Fryatt</t>
+          <t>Helen Dunn</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1157</t>
+          <t>1183</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rose Roché</t>
+          <t>Z Hayes</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1145</t>
+          <t>1179</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Helen Dunn</t>
+          <t>Anna Brown</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1144</t>
+          <t>1176</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Brian Tafazoli</t>
+          <t>Jason Jackson</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1140</t>
+          <t>1176</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Julie Jackson</t>
+          <t>Charles Myersberg</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1137</t>
+          <t>1171</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Luci Nguyen</t>
+          <t>Nic Faulds</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1124</t>
+          <t>1164</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Kim LastName</t>
+          <t>Alex LastName</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>1161</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Cassie Deering</t>
+          <t>Reagan Fryatt</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1114</t>
+          <t>1157</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Evan Sooklal</t>
+          <t>Harper Willingham</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1113</t>
+          <t>1155</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Piper Parker</t>
+          <t>Sakeena Saidou</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1111</t>
+          <t>1155</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Alexis Alms</t>
+          <t>Ronan McKinney</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>1152</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sam Tellis</t>
+          <t>Rose Roché</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1076</t>
+          <t>1145</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Noah Dale</t>
+          <t>Brian Tafazoli</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>1140</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>Julie Jackson</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>1137</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Graham Longhofer</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>1129</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Hares Ragub</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>1129</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Kim LastName</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>1117</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Luci Nguyen</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>1115</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Cassie Deering</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>1114</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Evan Sooklal</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>1113</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Piper Parker</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>1111</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Alexis Alms</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Sam Tellis</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>1076</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
           <t>Paul Bartenfeld</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>1006</t>
         </is>

--- a/exports/player_elo_table.xlsx
+++ b/exports/player_elo_table.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B58"/>
+  <dimension ref="A1:B59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>970</t>
         </is>
       </c>
     </row>
@@ -467,36 +467,36 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Aaron Carter</t>
+          <t>Milen Satish</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1385</t>
+          <t>1413</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Roman Ramirez</t>
+          <t>Aaron Carter</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1376</t>
+          <t>1385</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Milen Satish</t>
+          <t>Roman Ramirez</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1352</t>
+          <t>1376</t>
         </is>
       </c>
     </row>
@@ -515,108 +515,108 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ryan Healy</t>
+          <t>Cason Duszak</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1314</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kevin Cooper</t>
+          <t>Ryan Healy</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1307</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Autumn Hong</t>
+          <t>Ronan McKinney</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1295</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Nathan Snow</t>
+          <t>Bryce Taylor</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1276</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Bryce Taylor</t>
+          <t>Autumn Hong</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1272</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cason Duszak</t>
+          <t>Kevin Cooper</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1252</t>
+          <t>1272</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Will Simpson</t>
+          <t>Nathan Snow</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1244</t>
+          <t>1270</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Luke Woods</t>
+          <t>Will Simpson</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1241</t>
+          <t>1244</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Matthew Rusten</t>
+          <t>Luke Woods</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1238</t>
+          <t>1241</t>
         </is>
       </c>
     </row>
@@ -659,60 +659,60 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Eric Edwards</t>
+          <t>Benjamin Merkel</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1226</t>
+          <t>1225</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Leah Baetcke</t>
+          <t>Eric Edwards</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1217</t>
+          <t>1218</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Kristian Banlaoi</t>
+          <t>Leah Baetcke</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>1217</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Matthew Werfel</t>
+          <t>Kristian Banlaoi</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>1216</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Ann Hall</t>
+          <t>Matthew Werfel</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>1211</t>
         </is>
       </c>
     </row>
@@ -731,139 +731,139 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Connor Rogers</t>
+          <t>Ann Hall</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1208</t>
+          <t>1210</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Carolyn LastName</t>
+          <t>Connor Rogers</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1207</t>
+          <t>1208</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Yvonne Nguyen</t>
+          <t>Carolyn LastName</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1205</t>
+          <t>1207</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gabe Silverstein</t>
+          <t>Yvonne Nguyen</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1201</t>
+          <t>1205</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Carla Betancourt</t>
+          <t>Matthew Rusten</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1192</t>
+          <t>1202</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Benjamin Merkel</t>
+          <t>Gabe Silverstein</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1192</t>
+          <t>1201</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Victoria LastName</t>
+          <t>Carla Betancourt</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1191</t>
+          <t>1192</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Yafu LastName</t>
+          <t>Victoria LastName</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1191</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Maria Stalcup</t>
+          <t>Yafu LastName</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1184</t>
+          <t>1187</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Helen Dunn</t>
+          <t>Maria Stalcup</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1183</t>
+          <t>1184</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Z Hayes</t>
+          <t>Helen Dunn</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1179</t>
+          <t>1183</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Anna Brown</t>
+          <t>Jason Jackson</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -875,7 +875,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Jason Jackson</t>
+          <t>Anna Brown</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -899,31 +899,31 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Nic Faulds</t>
+          <t>Alex LastName</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1164</t>
+          <t>1161</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Alex LastName</t>
+          <t>Reagan Fryatt</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1161</t>
+          <t>1157</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Reagan Fryatt</t>
+          <t>Z Hayes</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -935,7 +935,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Harper Willingham</t>
+          <t>Sakeena Saidou</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -947,24 +947,24 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sakeena Saidou</t>
+          <t>Emily Allen</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>1152</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Ronan McKinney</t>
+          <t>Harper Willingham</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>1145</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Graham Longhofer</t>
+          <t>Hares Ragub</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1019,36 +1019,36 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Hares Ragub</t>
+          <t>Kim LastName</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>1117</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Kim LastName</t>
+          <t>Luci Nguyen</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>1115</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Luci Nguyen</t>
+          <t>Nic Faulds</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1115</t>
+          <t>1114</t>
         </is>
       </c>
     </row>
@@ -1079,24 +1079,24 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Piper Parker</t>
+          <t>Alexis Alms</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1111</t>
+          <t>1101</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Alexis Alms</t>
+          <t>Piper Parker</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>1095</t>
         </is>
       </c>
     </row>
@@ -1115,10 +1115,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>Graham Longhofer</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>1041</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
           <t>Paul Bartenfeld</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>1006</t>
         </is>
